--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="39" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>미라온휘트니스 천안두정점 헬스 PT 필라테스</t>
+          <t>365짐 천안두정점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>miraon2@naver.com</t>
+          <t>365gymdj@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1364-7983</t>
+          <t>0507-1391-3657</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 228 2층</t>
+          <t>충남 천안시 서북구 1공단1길 52 센트하임 2층 365짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miraon2</t>
+          <t>https://litt.ly/365gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uw1h</t>
+          <t>https://talk.naver.com/ct/w4xy9t</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>866</v>
+        <v>4146</v>
       </c>
       <c r="Q2" t="n">
-        <v>1409</v>
+        <v>2964</v>
       </c>
       <c r="R2" t="n">
-        <v>2275</v>
+        <v>7110</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1570105670</t>
+          <t>1490379364</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570105670</t>
+          <t>https://m.place.naver.com/place/1490379364</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>365짐 여성전용 헬스</t>
+          <t>미라온휘트니스 천안두정점 헬스 PT 필라테스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>365gymdj3@naver.com</t>
+          <t>miraon2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1494-3661</t>
+          <t>0507-1364-7983</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정역서3길 23 하이렉스타운 2층</t>
+          <t>충남 천안시 서북구 두정로 228 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://litt.ly/365gym3</t>
+          <t>https://blog.naver.com/miraon2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdlmk13</t>
+          <t>https://talk.naver.com/ct/w5uw1h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>989</v>
+        <v>864</v>
       </c>
       <c r="Q3" t="n">
-        <v>2483</v>
+        <v>1471</v>
       </c>
       <c r="R3" t="n">
-        <v>3472</v>
+        <v>2335</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1828895720</t>
+          <t>1570105670</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828895720</t>
+          <t>https://m.place.naver.com/place/1570105670</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>365짐 신부4호점</t>
+          <t>365짐 여성전용 헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>365gym__4@naver.com</t>
+          <t>365gymdj3@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1352-3658</t>
+          <t>0507-1494-3661</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 만남로 18 지하 1층 365짐</t>
+          <t>충남 천안시 서북구 두정역서3길 23 하이렉스타운 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://litt.ly/365gym4</t>
+          <t>https://litt.ly/365gym3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wejyiww</t>
+          <t>https://talk.naver.com/ct/wdlmk13</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1162</v>
+        <v>988</v>
       </c>
       <c r="Q4" t="n">
-        <v>2508</v>
+        <v>2505</v>
       </c>
       <c r="R4" t="n">
-        <v>3670</v>
+        <v>3493</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1585616197</t>
+          <t>1828895720</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1585616197</t>
+          <t>https://m.place.naver.com/place/1828895720</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>365짐 천안두정점</t>
+          <t>365짐 두정2호점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>365gymdj@naver.com</t>
+          <t>365gymdj2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1391-3657</t>
+          <t>0507-1447-3657</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 1공단1길 52 센트하임 2층 365짐</t>
+          <t>충남 천안시 서북구 서부대로 737 필레오 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/365gym</t>
+          <t>https://litt.ly/365gym2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4xy9t</t>
+          <t>https://talk.naver.com/ct/w4mjtt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4135</v>
+        <v>2498</v>
       </c>
       <c r="Q5" t="n">
-        <v>2943</v>
+        <v>2709</v>
       </c>
       <c r="R5" t="n">
-        <v>7078</v>
+        <v>5207</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1490379364</t>
+          <t>1717321794</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490379364</t>
+          <t>https://m.place.naver.com/place/1717321794</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엘투휘트니스 천안두정점</t>
+          <t>천안 쌍용동 헬스&amp;PT 미녀와야수짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>l2fitness@naver.com</t>
+          <t>dabinparks@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1382-3810</t>
+          <t>0507-1309-2118</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 노태산로 50 3층</t>
+          <t>충남 천안시 서북구 충무로 167-18 4층 미녀와야수짐 쌍용점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/l2fitness</t>
+          <t>https://blog.naver.com/dabinparks</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qtap</t>
+          <t>https://talk.naver.com/ct/w4e3s29</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1225</v>
+        <v>881</v>
       </c>
       <c r="Q6" t="n">
-        <v>1010</v>
+        <v>448</v>
       </c>
       <c r="R6" t="n">
-        <v>2235</v>
+        <v>1329</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1128929549</t>
+          <t>1103877507</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128929549</t>
+          <t>https://m.place.naver.com/place/1103877507</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="Q7" t="n">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="R7" t="n">
-        <v>981</v>
+        <v>998</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1216,10 +1216,10 @@
         <v>167</v>
       </c>
       <c r="Q8" t="n">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="R8" t="n">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jinh114@naver.com</t>
+          <t>zippy1999@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/crossfit_doklip/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1336,41 +1336,37 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유어짐 청당점</t>
+          <t>함마짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>your_gym@naver.com</t>
+          <t>hy_esoo@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1309-9270</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
+          <t>충남 천안시 서북구 두정로 166 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gym_hammar_boss</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,7 +1376,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1395,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wepzfrf</t>
+          <t>https://talk.naver.com/ct/w5urik</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q10" t="n">
-        <v>55</v>
+        <v>327</v>
       </c>
       <c r="R10" t="n">
-        <v>171</v>
+        <v>439</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2055460977</t>
+          <t>1163060455</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055460977</t>
+          <t>https://m.place.naver.com/place/1163060455</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1446,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공감PT여성전용공간 성정동점</t>
+          <t>유어짐 청당점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>djawndud99@naver.com</t>
+          <t>your_gym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1344-6267</t>
+          <t>0507-1309-9270</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
+          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggampt</t>
+          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ls51</t>
+          <t>https://talk.naver.com/ct/wepzfrf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="Q11" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="R11" t="n">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1159361767</t>
+          <t>2055460977</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159361767</t>
+          <t>https://m.place.naver.com/place/2055460977</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -628,10 +628,10 @@
         <v>4146</v>
       </c>
       <c r="Q2" t="n">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="R2" t="n">
-        <v>7110</v>
+        <v>7108</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미라온휘트니스 천안두정점 헬스 PT 필라테스</t>
+          <t>365짐 신부4호점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>miraon2@naver.com</t>
+          <t>365gym__4@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1364-7983</t>
+          <t>0507-1352-3658</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 228 2층</t>
+          <t>충남 천안시 동남구 만남로 18 지하 1층 365짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miraon2</t>
+          <t>https://litt.ly/365gym4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uw1h</t>
+          <t>https://talk.naver.com/ct/wejyiww</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>864</v>
+        <v>1174</v>
       </c>
       <c r="Q3" t="n">
-        <v>1471</v>
+        <v>2529</v>
       </c>
       <c r="R3" t="n">
-        <v>2335</v>
+        <v>3703</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1570105670</t>
+          <t>1585616197</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570105670</t>
+          <t>https://m.place.naver.com/place/1585616197</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="Q4" t="n">
-        <v>2505</v>
+        <v>2502</v>
       </c>
       <c r="R4" t="n">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>365짐 두정2호점</t>
+          <t>천안 쌍용동 헬스&amp;PT 미녀와야수짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>365gymdj2@naver.com</t>
+          <t>dabinparks@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1447-3657</t>
+          <t>0507-1309-2118</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부대로 737 필레오 4층</t>
+          <t>충남 천안시 서북구 충무로 167-18 4층 미녀와야수짐 쌍용점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/365gym2</t>
+          <t>https://blog.naver.com/dabinparks</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mjtt</t>
+          <t>https://talk.naver.com/ct/w4e3s29</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2498</v>
+        <v>884</v>
       </c>
       <c r="Q5" t="n">
-        <v>2709</v>
+        <v>449</v>
       </c>
       <c r="R5" t="n">
-        <v>5207</v>
+        <v>1333</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1717321794</t>
+          <t>1103877507</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717321794</t>
+          <t>https://m.place.naver.com/place/1103877507</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>천안 쌍용동 헬스&amp;PT 미녀와야수짐</t>
+          <t>365짐 두정2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dabinparks@naver.com</t>
+          <t>365gymdj2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1309-2118</t>
+          <t>0507-1447-3657</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 충무로 167-18 4층 미녀와야수짐 쌍용점</t>
+          <t>충남 천안시 서북구 서부대로 737 필레오 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dabinparks</t>
+          <t>https://litt.ly/365gym2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4e3s29</t>
+          <t>https://talk.naver.com/ct/w4mjtt</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>881</v>
+        <v>2498</v>
       </c>
       <c r="Q6" t="n">
-        <v>448</v>
+        <v>2709</v>
       </c>
       <c r="R6" t="n">
-        <v>1329</v>
+        <v>5207</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1103877507</t>
+          <t>1717321794</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1103877507</t>
+          <t>https://m.place.naver.com/place/1717321794</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Q7" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="R7" t="n">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,41 +1140,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
+          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teamspartagym_@naver.com</t>
+          <t>zippy1999@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1378-6132</t>
+          <t>0507-1404-6118</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
+          <t>충남 천안시 서북구 서부대로 762</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
+          <t>https://www.instagram.com/crossfit_doklip/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsr94</t>
+          <t>https://talk.naver.com/ct/w49qxi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="Q8" t="n">
-        <v>956</v>
+        <v>282</v>
       </c>
       <c r="R8" t="n">
-        <v>1123</v>
+        <v>351</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1197800655</t>
+          <t>34936808</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197800655</t>
+          <t>https://m.place.naver.com/place/34936808</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
+          <t>함마짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zippy1999@naver.com</t>
+          <t>hy_esoo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1404-6118</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부대로 762</t>
+          <t>충남 천안시 서북구 두정로 166 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit_doklip/</t>
+          <t>https://www.instagram.com/gym_hammar_boss</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49qxi</t>
+          <t>https://talk.naver.com/ct/w5urik</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="Q9" t="n">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="R9" t="n">
-        <v>351</v>
+        <v>437</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,47 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>34936808</t>
+          <t>1163060455</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34936808</t>
+          <t>https://m.place.naver.com/place/1163060455</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>유어짐 청당점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hy_esoo@naver.com</t>
+          <t>your_gym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1309-9270</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 166 4층</t>
+          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hammar_boss</t>
+          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5urik</t>
+          <t>https://talk.naver.com/ct/wepzfrf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="Q10" t="n">
-        <v>327</v>
+        <v>58</v>
       </c>
       <c r="R10" t="n">
-        <v>439</v>
+        <v>185</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1163060455</t>
+          <t>2055460977</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163060455</t>
+          <t>https://m.place.naver.com/place/2055460977</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유어짐 청당점</t>
+          <t>공감PT여성전용공간 성정동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>your_gym@naver.com</t>
+          <t>djawndud99@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1309-9270</t>
+          <t>0507-1344-6267</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
+          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
+          <t>https://linktr.ee/gonggampt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wepzfrf</t>
+          <t>https://talk.naver.com/ct/w4ls51</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="Q11" t="n">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="R11" t="n">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2055460977</t>
+          <t>1159361767</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055460977</t>
+          <t>https://m.place.naver.com/place/1159361767</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -824,10 +824,10 @@
         <v>992</v>
       </c>
       <c r="Q4" t="n">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="R4" t="n">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>2498</v>
       </c>
       <c r="Q6" t="n">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="R6" t="n">
-        <v>5207</v>
+        <v>5206</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hy_esoo@naver.com</t>
+          <t>soyoung_lee1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>

--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -628,10 +628,10 @@
         <v>4146</v>
       </c>
       <c r="Q2" t="n">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="R2" t="n">
-        <v>7108</v>
+        <v>7106</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         <v>992</v>
       </c>
       <c r="Q4" t="n">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="R4" t="n">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -858,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>천안 쌍용동 헬스&amp;PT 미녀와야수짐</t>
+          <t>365짐 두정2호점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dabinparks@naver.com</t>
+          <t>365gymdj2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1309-2118</t>
+          <t>0507-1447-3657</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 충무로 167-18 4층 미녀와야수짐 쌍용점</t>
+          <t>충남 천안시 서북구 서부대로 737 필레오 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dabinparks</t>
+          <t>https://litt.ly/365gym2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4e3s29</t>
+          <t>https://talk.naver.com/ct/w4mjtt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>884</v>
+        <v>2498</v>
       </c>
       <c r="Q5" t="n">
-        <v>449</v>
+        <v>2706</v>
       </c>
       <c r="R5" t="n">
-        <v>1333</v>
+        <v>5204</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1103877507</t>
+          <t>1717321794</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1103877507</t>
+          <t>https://m.place.naver.com/place/1717321794</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>365짐 두정2호점</t>
+          <t>천안 쌍용동 헬스&amp;PT 미녀와야수짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>365gymdj2@naver.com</t>
+          <t>dabinparks@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1447-3657</t>
+          <t>0507-1309-2118</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부대로 737 필레오 4층</t>
+          <t>충남 천안시 서북구 충무로 167-18 4층 미녀와야수짐 쌍용점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://litt.ly/365gym2</t>
+          <t>https://blog.naver.com/dabinparks</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mjtt</t>
+          <t>https://talk.naver.com/ct/w4e3s29</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2498</v>
+        <v>884</v>
       </c>
       <c r="Q6" t="n">
-        <v>2708</v>
+        <v>450</v>
       </c>
       <c r="R6" t="n">
-        <v>5206</v>
+        <v>1334</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1717321794</t>
+          <t>1103877507</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717321794</t>
+          <t>https://m.place.naver.com/place/1103877507</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1147,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
+          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>zippy1999@naver.com</t>
+          <t>teamspartagym_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1404-6118</t>
+          <t>0507-1378-6132</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부대로 762</t>
+          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit_doklip/</t>
+          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49qxi</t>
+          <t>https://talk.naver.com/ct/wcsr94</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="Q8" t="n">
-        <v>282</v>
+        <v>957</v>
       </c>
       <c r="R8" t="n">
-        <v>351</v>
+        <v>1124</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>34936808</t>
+          <t>1197800655</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34936808</t>
+          <t>https://m.place.naver.com/place/1197800655</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,25 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>soyoung_lee1@naver.com</t>
+          <t>zippy1999@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1404-6118</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 166 4층</t>
+          <t>충남 천안시 서북구 서부대로 762</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hammar_boss</t>
+          <t>https://www.instagram.com/crossfit_doklip/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5urik</t>
+          <t>https://talk.naver.com/ct/w49qxi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="Q9" t="n">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="R9" t="n">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1163060455</t>
+          <t>34936808</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163060455</t>
+          <t>https://m.place.naver.com/place/34936808</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -726,10 +726,10 @@
         <v>1174</v>
       </c>
       <c r="Q3" t="n">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="R3" t="n">
-        <v>3703</v>
+        <v>3704</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="Q6" t="n">
         <v>450</v>
       </c>
       <c r="R6" t="n">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         <v>514</v>
       </c>
       <c r="Q7" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="R7" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1147,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
+          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teamspartagym_@naver.com</t>
+          <t>zippy1999@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1378-6132</t>
+          <t>0507-1404-6118</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
+          <t>충남 천안시 서북구 서부대로 762</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
+          <t>https://www.instagram.com/crossfit_doklip/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsr94</t>
+          <t>https://talk.naver.com/ct/w49qxi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="Q8" t="n">
-        <v>957</v>
+        <v>282</v>
       </c>
       <c r="R8" t="n">
-        <v>1124</v>
+        <v>351</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1197800655</t>
+          <t>34936808</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197800655</t>
+          <t>https://m.place.naver.com/place/34936808</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1250,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
+          <t>함마짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zippy1999@naver.com</t>
+          <t>soyoung_lee1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1404-6118</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부대로 762</t>
+          <t>충남 천안시 서북구 두정로 166 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit_doklip/</t>
+          <t>https://www.instagram.com/gym_hammar_boss</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49qxi</t>
+          <t>https://talk.naver.com/ct/w5urik</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="Q9" t="n">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="R9" t="n">
-        <v>351</v>
+        <v>437</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>34936808</t>
+          <t>1163060455</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34936808</t>
+          <t>https://m.place.naver.com/place/1163060455</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4146</v>
+        <v>4144</v>
       </c>
       <c r="Q2" t="n">
         <v>2960</v>
       </c>
       <c r="R2" t="n">
-        <v>7106</v>
+        <v>7104</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1140,41 +1140,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
+          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>zippy1999@naver.com</t>
+          <t>teamspartagym_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1404-6118</t>
+          <t>0507-1378-6132</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부대로 762</t>
+          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit_doklip/</t>
+          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49qxi</t>
+          <t>https://talk.naver.com/ct/wcsr94</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="Q8" t="n">
-        <v>282</v>
+        <v>957</v>
       </c>
       <c r="R8" t="n">
-        <v>351</v>
+        <v>1124</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>34936808</t>
+          <t>1197800655</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34936808</t>
+          <t>https://m.place.naver.com/place/1197800655</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1250,25 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>soyoung_lee1@naver.com</t>
+          <t>zippy1999@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1404-6118</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 166 4층</t>
+          <t>충남 천안시 서북구 서부대로 762</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hammar_boss</t>
+          <t>https://www.instagram.com/crossfit_doklip/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5urik</t>
+          <t>https://talk.naver.com/ct/w49qxi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="Q9" t="n">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="R9" t="n">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1163060455</t>
+          <t>34936808</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163060455</t>
+          <t>https://m.place.naver.com/place/34936808</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1434,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1532,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -628,10 +628,10 @@
         <v>4144</v>
       </c>
       <c r="Q2" t="n">
-        <v>2960</v>
+        <v>2962</v>
       </c>
       <c r="R2" t="n">
-        <v>7104</v>
+        <v>7106</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         <v>1174</v>
       </c>
       <c r="Q3" t="n">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="R3" t="n">
-        <v>3704</v>
+        <v>3705</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         <v>992</v>
       </c>
       <c r="Q4" t="n">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="R4" t="n">
-        <v>3491</v>
+        <v>3492</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         <v>2498</v>
       </c>
       <c r="Q5" t="n">
-        <v>2706</v>
+        <v>2705</v>
       </c>
       <c r="R5" t="n">
-        <v>5204</v>
+        <v>5203</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="Q2" t="n">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="R2" t="n">
-        <v>3706</v>
+        <v>3705</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         <v>4144</v>
       </c>
       <c r="Q3" t="n">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="R3" t="n">
-        <v>7104</v>
+        <v>7103</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="Q4" t="n">
         <v>2499</v>
       </c>
       <c r="R4" t="n">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>미라온휘트니스 천안두정점 헬스 PT 필라테스</t>
+          <t>퓨처휘트니스 청당 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>miraon2@naver.com</t>
+          <t>futurefit@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1364-7983</t>
+          <t>0507-1457-2391</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 228 2층</t>
+          <t>충남 천안시 동남구 청수14로 102 에이스법조타워 3층 301~309호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miraon2</t>
+          <t>https://blog.naver.com/futurefit</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uw1h</t>
+          <t>https://talk.naver.com/ct/w4wi8w</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>865</v>
+        <v>937</v>
       </c>
       <c r="Q5" t="n">
-        <v>1490</v>
+        <v>825</v>
       </c>
       <c r="R5" t="n">
-        <v>2355</v>
+        <v>1762</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1570105670</t>
+          <t>1704647072</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570105670</t>
+          <t>https://m.place.naver.com/place/1704647072</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>365짐 두정2호점</t>
+          <t>미라온휘트니스 천안두정점 헬스 PT 필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>365gymdj2@naver.com</t>
+          <t>miraon2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1447-3657</t>
+          <t>0507-1364-7983</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부대로 737 필레오 4층</t>
+          <t>충남 천안시 서북구 두정로 228 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://litt.ly/365gym2</t>
+          <t>https://blog.naver.com/miraon2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mjtt</t>
+          <t>https://talk.naver.com/ct/w5uw1h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2499</v>
+        <v>865</v>
       </c>
       <c r="Q6" t="n">
-        <v>2705</v>
+        <v>1494</v>
       </c>
       <c r="R6" t="n">
-        <v>5204</v>
+        <v>2359</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1717321794</t>
+          <t>1570105670</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1717321794</t>
+          <t>https://m.place.naver.com/place/1570105670</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
+          <t>W GYM 두정점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>zippy1999@naver.com</t>
+          <t>wok5685@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1404-6118</t>
+          <t>0507-1446-7330</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부대로 762</t>
+          <t>충남 천안시 서북구 천안대로 1024-5 2층 W GYM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit_doklip/</t>
+          <t>https://blog.naver.com/wok5685</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49qxi</t>
+          <t>https://talk.naver.com/ct/w46rpz</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>69</v>
+        <v>305</v>
       </c>
       <c r="Q7" t="n">
-        <v>282</v>
+        <v>531</v>
       </c>
       <c r="R7" t="n">
-        <v>351</v>
+        <v>836</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>34936808</t>
+          <t>1895436736</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34936808</t>
+          <t>https://m.place.naver.com/place/1895436736</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,25 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hy_esoo@naver.com</t>
+          <t>zippy1999@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1404-6118</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 166 4층</t>
+          <t>충남 천안시 서북구 서부대로 762</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hammar_boss</t>
+          <t>https://www.instagram.com/crossfit_doklip/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1195,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5urik</t>
+          <t>https://talk.naver.com/ct/w49qxi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="Q8" t="n">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="R8" t="n">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1163060455</t>
+          <t>34936808</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163060455</t>
+          <t>https://m.place.naver.com/place/34936808</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,29 +1250,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라이언스짐 쌍용동 헬스&amp;PT</t>
+          <t>함마짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lionsgyme@naver.com</t>
+          <t>hy_esoo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1344-8444</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 월봉로 90 3층</t>
+          <t>충남 천안시 서북구 두정로 166 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lionsgyme</t>
+          <t>https://www.instagram.com/gym_hammar_boss</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdfujfr</t>
+          <t>https://talk.naver.com/ct/w5urik</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>649</v>
+        <v>110</v>
       </c>
       <c r="Q9" t="n">
-        <v>181</v>
+        <v>327</v>
       </c>
       <c r="R9" t="n">
-        <v>830</v>
+        <v>437</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1674228677</t>
+          <t>1163060455</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674228677</t>
+          <t>https://m.place.naver.com/place/1163060455</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에스엠바디짐 신부점</t>
+          <t>유어짐 청당점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>scuzy8088@naver.com</t>
+          <t>your_gym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1486-4288</t>
+          <t>0507-1309-9270</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 단대로 70 2층</t>
+          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/scuzy8088?tab=1</t>
+          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wyt0aa9</t>
+          <t>https://talk.naver.com/ct/wepzfrf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>806</v>
+        <v>128</v>
       </c>
       <c r="Q10" t="n">
-        <v>826</v>
+        <v>59</v>
       </c>
       <c r="R10" t="n">
-        <v>1632</v>
+        <v>187</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1531238237</t>
+          <t>2055460977</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1531238237</t>
+          <t>https://m.place.naver.com/place/2055460977</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유어짐 청당점</t>
+          <t>공감PT여성전용공간 성정동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>your_gym@naver.com</t>
+          <t>djawndud99@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1309-9270</t>
+          <t>0507-1344-6267</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
+          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
+          <t>https://linktr.ee/gonggampt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wepzfrf</t>
+          <t>https://talk.naver.com/ct/w4ls51</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="Q11" t="n">
-        <v>59</v>
+        <v>162</v>
       </c>
       <c r="R11" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2055460977</t>
+          <t>1159361767</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055460977</t>
+          <t>https://m.place.naver.com/place/1159361767</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4144</v>
+        <v>4145</v>
       </c>
       <c r="Q3" t="n">
         <v>2959</v>
       </c>
       <c r="R3" t="n">
-        <v>7103</v>
+        <v>7104</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="Q5" t="n">
         <v>825</v>
       </c>
       <c r="R5" t="n">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>W GYM 두정점</t>
+          <t>365일 24시 짐그로우 쌍용역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wok5685@naver.com</t>
+          <t>gymgrow@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1446-7330</t>
+          <t>0507-1465-3657</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 천안대로 1024-5 2층 W GYM</t>
+          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wok5685</t>
+          <t>https://blog.naver.com/gymgrow/223761915716</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46rpz</t>
+          <t>https://talk.naver.com/ct/w5w7k9</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>305</v>
+        <v>516</v>
       </c>
       <c r="Q7" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="R7" t="n">
-        <v>836</v>
+        <v>1004</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1895436736</t>
+          <t>1256642880</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895436736</t>
+          <t>https://m.place.naver.com/place/1256642880</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/천안_헬스장.xlsx
+++ b/naver-place-crawler/results_health/천안_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -824,10 +824,10 @@
         <v>991</v>
       </c>
       <c r="Q4" t="n">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="R4" t="n">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1147,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
+          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>zippy1999@naver.com</t>
+          <t>teamspartagym_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1404-6118</t>
+          <t>0507-1378-6132</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부대로 762</t>
+          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit_doklip/</t>
+          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49qxi</t>
+          <t>https://talk.naver.com/ct/wcsr94</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="Q8" t="n">
-        <v>282</v>
+        <v>959</v>
       </c>
       <c r="R8" t="n">
-        <v>351</v>
+        <v>1126</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>34936808</t>
+          <t>1197800655</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34936808</t>
+          <t>https://m.place.naver.com/place/1197800655</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,25 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>크로스핏 독립 트레이닝 센터 천안 두정점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hy_esoo@naver.com</t>
+          <t>zippy1999@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1404-6118</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 166 4층</t>
+          <t>충남 천안시 서북구 서부대로 762</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hammar_boss</t>
+          <t>https://www.instagram.com/crossfit_doklip/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5urik</t>
+          <t>https://talk.naver.com/ct/w49qxi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="Q9" t="n">
-        <v>327</v>
+        <v>282</v>
       </c>
       <c r="R9" t="n">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1163060455</t>
+          <t>34936808</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163060455</t>
+          <t>https://m.place.naver.com/place/34936808</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1459,7 +1463,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
+          <t>충남 천안시 서북구 성��두정로 38 4층 401호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
